--- a/khmodm/src/main/resources/treading-water.xlsx
+++ b/khmodm/src/main/resources/treading-water.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/NetBeansProjects/taichidm/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/GitHub/KHMOntology/khmodm/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA75B43-2F0E-3A46-8708-D9293241EA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16F3551-3615-5648-A528-F408A77B3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="6260" windowWidth="38400" windowHeight="23500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Treading Water" sheetId="7" r:id="rId1"/>
@@ -193,9 +193,6 @@
 Hip Abductors-Rotation;</t>
   </si>
   <si>
-    <t xml:space="preserve"> Deltoids; Latissimus Dorsi; Trapezius; Biceps Brachii; Triceps Brachii; Rectus Abdominis; Obliques; Iliopsoas; Quadriceps: Gluteus Maximus; Hamstrings; Gastrocnemius; Soleus</t>
-  </si>
-  <si>
     <r>
       <t>Deltoids; latissimus dorsi; trapezius; biceps brachii; triceps brachii</t>
     </r>
@@ -245,6 +242,9 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deltoids; Latissimus Dorsi; Trapezius; Biceps Brachii; Triceps Brachii; Rectus Abdominis; Obliques; Iliopsoas; Quadriceps; Gluteus Maximus; Hamstrings; Gastrocnemius; Soleus</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="16">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>13</v>
@@ -828,7 +828,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>15</v>
@@ -839,7 +839,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="333.75" customHeight="1">
@@ -853,7 +853,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -862,7 +862,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>21</v>
